--- a/per-stock/ETR/financials.xlsx
+++ b/per-stock/ETR/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49923403776</v>
+        <v>50875809792</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80714629120</v>
+        <v>81666924544</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.743002</v>
+        <v>28.344387</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.696606</v>
+        <v>21.947784</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.757188</v>
+        <v>3.828865</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-3913097728</v>
+        <v>-3150947000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>109.03</v>
+        <v>111.11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -790,988 +799,465 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Line item</t>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>FY-3</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>FY-2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>FY-1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
+          <t>TTM</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>Source / formula</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tax Effect Of Unusual Items</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>36776889</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>6840768</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>11720940</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>49622160</v>
-      </c>
-      <c r="F2" s="3" t="n"/>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tax Rate For Calcs</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F3" s="3" t="n"/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D47</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C47</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B47</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B47:E47)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Normalized EBITDA</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>5977138000</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>5010681000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>4866846000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>4000053000</v>
-      </c>
-      <c r="F4" s="3" t="n"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D45</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C45</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B45</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total Unusual Items</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>167931000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>25912000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>55814000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>236296000</v>
-      </c>
-      <c r="F5" s="3" t="n"/>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total Unusual Items Excluding Goodwill</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>167931000</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>25912000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>55814000</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>236296000</v>
-      </c>
-      <c r="F6" s="3" t="n"/>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Net Income From Continuing Operation Net Minority Interest</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1773328000</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1061184000</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>2362310000</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1097138000</v>
-      </c>
-      <c r="F7" s="3" t="n"/>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reconciled Depreciation</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>2537138000</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>2443562000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>2244479000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>2190371000</v>
-      </c>
-      <c r="F8" s="3" t="n"/>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reconciled Cost Of Revenue</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>6309481000</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>5710972000</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>6418500000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>8059538000</v>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>6145069000</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>5036593000</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>4922660000</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>4236349000</v>
-      </c>
-      <c r="F10" s="3" t="n"/>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>3607931000</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>2593031000</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>2678181000</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>2045978000</v>
-      </c>
-      <c r="F11" s="3" t="n"/>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Net Interest Income</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-1019303000</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>-851955000</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>-843680000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-987818000</v>
-      </c>
-      <c r="F12" s="3" t="n"/>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Interest Expense</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>1336651000</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>1150820000</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1006406000</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>987818000</v>
-      </c>
-      <c r="F13" s="3" t="n"/>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>317348000</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>298865000</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>162726000</v>
-      </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n">
-        <v>430466000</v>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Normalized Income</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1642173889</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>1042112768</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>2318216940</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>910464160</v>
-      </c>
-      <c r="F15" s="3" t="n"/>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Net Income From Continuing And Discontinued Operation</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1773328000</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1061184000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>2362310000</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>1097138000</v>
-      </c>
-      <c r="F16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>9731613000</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>9121429000</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>9486758000</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>11876926000</v>
-      </c>
-      <c r="F17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Total Operating Income As Reported</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>3202278000</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>2651090000</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>2617975000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>2050775000</v>
-      </c>
-      <c r="F18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Diluted Average Shares</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>450151884</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>431581696</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>424752990</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>411095156</v>
-      </c>
-      <c r="F19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Basic Average Shares</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>442029481</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>427713121</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>423139862</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>408900708</v>
-      </c>
-      <c r="F20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Diluted EPS</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>2.685</v>
-      </c>
-      <c r="F21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Basic EPS</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Diluted NI Availto Com Stockholders</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>1758272000</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>1055590000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>2356536000</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>1103166000</v>
-      </c>
-      <c r="F23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Net Income Common Stockholders</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>1758272000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1055590000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>2356536000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>1103166000</v>
-      </c>
-      <c r="F24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Preferred Stock Dividends</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>15056000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>5594000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>5774000</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-6028000</v>
-      </c>
-      <c r="F25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>1773328000</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>1061184000</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>2362310000</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1097138000</v>
-      </c>
-      <c r="F26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Net Income Including Noncontrolling Interests</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>1773328000</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1061184000</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>2362310000</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>1097138000</v>
-      </c>
-      <c r="F27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Net Income Continuous Operations</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>1773328000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1061184000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>2362310000</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>1097138000</v>
-      </c>
-      <c r="F28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Tax Provision</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>497952000</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>381027000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>-690535000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-38978000</v>
-      </c>
-      <c r="F29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pretax Income</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>2271280000</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1442211000</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>1671775000</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>1058160000</v>
-      </c>
-      <c r="F30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Other Income Expense</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>75510000</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>-464058000</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>-145199000</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>158667000</v>
-      </c>
-      <c r="F31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Other Non Operating Income Expenses</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>-92421000</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>-489970000</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>-201013000</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-77629000</v>
-      </c>
-      <c r="F32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Special Income Charges</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>167931000</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>25912000</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>55814000</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>236296000</v>
-      </c>
-      <c r="F33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Other Special Charges</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>-180726000</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>-133046000</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>-98493000</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-72832000</v>
-      </c>
-      <c r="F34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Write Off</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>12795000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>107134000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>42679000</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-163464000</v>
-      </c>
-      <c r="F35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Net Non Operating Interest Income Expense</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>-1019303000</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>-851955000</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>-843680000</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>-987818000</v>
-      </c>
-      <c r="F36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Interest Expense Non Operating</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>1336651000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>1150820000</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>1006406000</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>987818000</v>
-      </c>
-      <c r="F37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Interest Income Non Operating</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>317348000</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>298865000</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>162726000</v>
-      </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n">
-        <v>430466000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Operating Income</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>3215073000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>2758224000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>2660654000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>1887311000</v>
-      </c>
-      <c r="F39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>2962686000</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>2980063000</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>2668782000</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>3388040000</v>
-      </c>
-      <c r="F40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Other Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>66330000</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>213947000</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>68205000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>893479000</v>
-      </c>
-      <c r="F41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Other Taxes</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>818664000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>752948000</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>755574000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>733538000</v>
-      </c>
-      <c r="F42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Depreciation Amortization Depletion Income Statement</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>2077692000</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>2013168000</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>1845003000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>1761023000</v>
-      </c>
-      <c r="F43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Depreciation And Amortization In Income Statement</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>2077692000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>2013168000</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>1845003000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>1761023000</v>
-      </c>
-      <c r="F44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>6177759000</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>5738287000</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>5329436000</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>5275351000</v>
-      </c>
-      <c r="F45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cost Of Revenue</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>6768927000</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>6141366000</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>6817976000</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>8488886000</v>
-      </c>
-      <c r="F46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>12946686000</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>11879653000</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>12147412000</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>13764237000</v>
-      </c>
-      <c r="F47" s="3" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>12887921000</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>11805802000</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>12022944000</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>13420765000</v>
-      </c>
-      <c r="F48" s="3" t="n"/>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1803,27 +1289,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-12-31</t>
         </is>
       </c>
     </row>
@@ -1834,20 +1320,18 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5358423</v>
+        <v>36776889</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5796177.489457</v>
+        <v>6840768</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9327884</v>
+        <v>11720940</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>11646235</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>9507888</v>
-      </c>
+        <v>49622160</v>
+      </c>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1856,20 +1340,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.183</v>
+        <v>0.219</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.183912</v>
+        <v>0.264</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.227</v>
+        <v>0.21</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.216</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1878,20 +1360,18 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1483723000</v>
+        <v>5977138000</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1258855000</v>
+        <v>5010681000</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1833721000</v>
+        <v>4866846000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1513760000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1370802000</v>
-      </c>
+        <v>4000053000</v>
+      </c>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1900,20 +1380,18 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>29281000</v>
+        <v>167931000</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>31516000</v>
+        <v>25912000</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>41092000</v>
+        <v>55814000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>51305000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>44018000</v>
-      </c>
+        <v>236296000</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1922,20 +1400,18 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>29281000</v>
+        <v>167931000</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>31516000</v>
+        <v>25912000</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>41092000</v>
+        <v>55814000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>51305000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>44018000</v>
-      </c>
+        <v>236296000</v>
+      </c>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1944,20 +1420,18 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>390805000</v>
+        <v>1773328000</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>240528000</v>
+        <v>1061184000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>698424000</v>
+        <v>2362310000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>471954000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>362422000</v>
-      </c>
+        <v>1097138000</v>
+      </c>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1966,20 +1440,18 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>654669000</v>
+        <v>2537138000</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>635730000</v>
+        <v>2443562000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>646204000</v>
+        <v>2244479000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>632638000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>622566000</v>
-      </c>
+        <v>2190371000</v>
+      </c>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1988,20 +1460,18 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1558035000</v>
+        <v>6309481000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1598618000</v>
+        <v>5710972000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1768110000</v>
+        <v>6418500000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1656400000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1286353000</v>
-      </c>
+        <v>8059538000</v>
+      </c>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2010,20 +1480,18 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1513004000</v>
+        <v>6145069000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1290371000</v>
+        <v>5036593000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1874813000</v>
+        <v>4922660000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1565065000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1414820000</v>
-      </c>
+        <v>4236349000</v>
+      </c>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2032,20 +1500,18 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>858335000</v>
+        <v>3607931000</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>654641000</v>
+        <v>2593031000</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1228609000</v>
+        <v>2678181000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>932427000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>792254000</v>
-      </c>
+        <v>2045978000</v>
+      </c>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2054,20 +1520,18 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-163930000</v>
+        <v>-1019303000</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-269475000</v>
+        <v>-851955000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-218788000</v>
+        <v>-843680000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-234655000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-296385000</v>
-      </c>
+        <v>-987818000</v>
+      </c>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2076,20 +1540,18 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>379740000</v>
+        <v>1336651000</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>359908000</v>
+        <v>1150820000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>324878000</v>
+        <v>1006406000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>322074000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>329791000</v>
-      </c>
+        <v>987818000</v>
+      </c>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2098,19 +1560,17 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>215810000</v>
+        <v>317348000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>90433000</v>
+        <v>298865000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>106090000</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>87419000</v>
-      </c>
+        <v>162726000</v>
+      </c>
+      <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n">
-        <v>33406000</v>
+        <v>430466000</v>
       </c>
     </row>
     <row r="15">
@@ -2120,20 +1580,18 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>366882423</v>
+        <v>1642173889</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>214808177.489457</v>
+        <v>1042112768</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>666659884</v>
+        <v>2318216940</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>432295235</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>327911888</v>
-      </c>
+        <v>910464160</v>
+      </c>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2142,20 +1600,18 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>390805000</v>
+        <v>1773328000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>240528000</v>
+        <v>1061184000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>698424000</v>
+        <v>2362310000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>471954000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>362422000</v>
-      </c>
+        <v>1097138000</v>
+      </c>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2164,20 +1620,18 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2597345000</v>
+        <v>9731613000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2413236000</v>
+        <v>9121429000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2680183000</v>
+        <v>9486758000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2491424000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>2146770000</v>
-      </c>
+        <v>11876926000</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2186,20 +1640,18 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>572222000</v>
+        <v>3202278000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>545708000</v>
+        <v>2651090000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1119041000</v>
+        <v>2617975000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>837425000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>700104000</v>
-      </c>
+        <v>2050775000</v>
+      </c>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2208,20 +1660,18 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>462510666</v>
+        <v>450151884</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>458602768</v>
+        <v>431581696</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>453550895</v>
+        <v>424752990</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>445700889</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>440648342</v>
-      </c>
+        <v>411095156</v>
+      </c>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2230,20 +1680,18 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>455717833</v>
+        <v>442029481</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>451770241</v>
+        <v>427713121</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>446532648</v>
+        <v>423139862</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>439182369</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>430347768</v>
-      </c>
+        <v>408900708</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2252,20 +1700,18 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.83</v>
+        <v>3.91</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.51</v>
+        <v>2.45</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.53</v>
+        <v>5.55</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.82</v>
-      </c>
+        <v>2.685</v>
+      </c>
+      <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2274,20 +1720,18 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.84</v>
+        <v>3.98</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.52</v>
+        <v>2.47</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.55</v>
+        <v>5.57</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.84</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="F22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2296,20 +1740,18 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>384916000</v>
+        <v>1758272000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>235782000</v>
+        <v>1055590000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>693800000</v>
+        <v>2356536000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>467930000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>360760000</v>
-      </c>
+        <v>1103166000</v>
+      </c>
+      <c r="F23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2318,20 +1760,18 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>384916000</v>
+        <v>1758272000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>235782000</v>
+        <v>1055590000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>693800000</v>
+        <v>2356536000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>467930000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>360760000</v>
-      </c>
+        <v>1103166000</v>
+      </c>
+      <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2340,20 +1780,18 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5889000</v>
+        <v>15056000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>4746000</v>
+        <v>5594000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4624000</v>
+        <v>5774000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4024000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>1662000</v>
-      </c>
+        <v>-6028000</v>
+      </c>
+      <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2362,20 +1800,18 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>390805000</v>
+        <v>1773328000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>240528000</v>
+        <v>1061184000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>698424000</v>
+        <v>2362310000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>471954000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>362422000</v>
-      </c>
+        <v>1097138000</v>
+      </c>
+      <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2384,20 +1820,18 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>390805000</v>
+        <v>1773328000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>240528000</v>
+        <v>1061184000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>698424000</v>
+        <v>2362310000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>471954000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>362422000</v>
-      </c>
+        <v>1097138000</v>
+      </c>
+      <c r="F27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2406,20 +1840,18 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>390805000</v>
+        <v>1773328000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>240528000</v>
+        <v>1061184000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>698424000</v>
+        <v>2362310000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>471954000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>362422000</v>
-      </c>
+        <v>1097138000</v>
+      </c>
+      <c r="F28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2428,20 +1860,18 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>87790000</v>
+        <v>497952000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>54205000</v>
+        <v>381027000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>205307000</v>
+        <v>-690535000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>138399000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>100041000</v>
-      </c>
+        <v>-38978000</v>
+      </c>
+      <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2450,20 +1880,18 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>478595000</v>
+        <v>2271280000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>294733000</v>
+        <v>1442211000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>903731000</v>
+        <v>1671775000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>610353000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>462463000</v>
-      </c>
+        <v>1058160000</v>
+      </c>
+      <c r="F30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2472,20 +1900,18 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>52244000</v>
+        <v>75510000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>18500000</v>
+        <v>-464058000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-9317000</v>
+        <v>-145199000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>7583000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>58744000</v>
-      </c>
+        <v>158667000</v>
+      </c>
+      <c r="F31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2494,20 +1920,18 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>22963000</v>
+        <v>-92421000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-13016000</v>
+        <v>-489970000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-50409000</v>
+        <v>-201013000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-43722000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>14726000</v>
-      </c>
+        <v>-77629000</v>
+      </c>
+      <c r="F32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2516,20 +1940,18 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>29281000</v>
+        <v>167931000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>31516000</v>
+        <v>25912000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>41092000</v>
+        <v>55814000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>51305000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>44018000</v>
-      </c>
+        <v>236296000</v>
+      </c>
+      <c r="F33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2538,20 +1960,18 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-47340000</v>
+        <v>-180726000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-31516000</v>
+        <v>-133046000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-53887000</v>
+        <v>-98493000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-51305000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>-44018000</v>
-      </c>
+        <v>-72832000</v>
+      </c>
+      <c r="F34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2560,20 +1980,18 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>18059000</v>
+        <v>12795000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>107134000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>12795000</v>
+        <v>42679000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-163464000</v>
+      </c>
+      <c r="F35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2582,20 +2000,18 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-163930000</v>
+        <v>-1019303000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-269475000</v>
+        <v>-851955000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-218788000</v>
+        <v>-843680000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-234655000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>-296385000</v>
-      </c>
+        <v>-987818000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2604,20 +2020,18 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>379740000</v>
+        <v>1336651000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>359908000</v>
+        <v>1150820000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>324878000</v>
+        <v>1006406000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>322074000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>329791000</v>
-      </c>
+        <v>987818000</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2626,19 +2040,17 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>215810000</v>
+        <v>317348000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>90433000</v>
+        <v>298865000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>106090000</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>87419000</v>
-      </c>
+        <v>162726000</v>
+      </c>
+      <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n">
-        <v>33406000</v>
+        <v>430466000</v>
       </c>
     </row>
     <row r="39">
@@ -2648,20 +2060,18 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>590281000</v>
+        <v>3215073000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>545708000</v>
+        <v>2758224000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1131836000</v>
+        <v>2660654000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>837425000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>700104000</v>
-      </c>
+        <v>1887311000</v>
+      </c>
+      <c r="F39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2670,20 +2080,18 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>924770000</v>
+        <v>2962686000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>695669000</v>
+        <v>2980063000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>791254000</v>
+        <v>2668782000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>724969000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>750794000</v>
-      </c>
+        <v>3388040000</v>
+      </c>
+      <c r="F40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2692,20 +2100,18 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>178117000</v>
+        <v>66330000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-6866000</v>
+        <v>213947000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>33498000</v>
+        <v>68205000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>612000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>39086000</v>
-      </c>
+        <v>893479000</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2714,20 +2120,18 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>206524000</v>
+        <v>818664000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>185754000</v>
+        <v>752948000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>232371000</v>
+        <v>755574000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>201774000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>198765000</v>
-      </c>
+        <v>733538000</v>
+      </c>
+      <c r="F42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2736,20 +2140,18 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>540129000</v>
+        <v>2077692000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>516781000</v>
+        <v>2013168000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>525385000</v>
+        <v>1845003000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>522583000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>512943000</v>
-      </c>
+        <v>1761023000</v>
+      </c>
+      <c r="F43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2758,20 +2160,18 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>540129000</v>
+        <v>2077692000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>516781000</v>
+        <v>2013168000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>525385000</v>
+        <v>1845003000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>522583000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>512943000</v>
-      </c>
+        <v>1761023000</v>
+      </c>
+      <c r="F44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2780,20 +2180,18 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>1515051000</v>
+        <v>6177759000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1241377000</v>
+        <v>5738287000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1923090000</v>
+        <v>5329436000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1562394000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>1450898000</v>
-      </c>
+        <v>5275351000</v>
+      </c>
+      <c r="F45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2802,20 +2200,18 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>1672575000</v>
+        <v>6768927000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1717567000</v>
+        <v>6141366000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1888929000</v>
+        <v>6817976000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1766455000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>1395976000</v>
-      </c>
+        <v>8488886000</v>
+      </c>
+      <c r="F46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2824,20 +2220,18 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>3187626000</v>
+        <v>12946686000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2958944000</v>
+        <v>11879653000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>3812019000</v>
+        <v>12147412000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>3328849000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>2846874000</v>
-      </c>
+        <v>13764237000</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2846,20 +2240,18 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3170273000</v>
+        <v>12887921000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2900179000</v>
+        <v>11805802000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3812019000</v>
+        <v>12022944000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3315723000</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>2829597000</v>
-      </c>
+        <v>13420765000</v>
+      </c>
+      <c r="F48" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2867,6 +2259,1094 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tax Effect Of Unusual Items</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>5358423</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>5796177.489457</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>9327884</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>11646235</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>9507888</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tax Rate For Calcs</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.183912</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Normalized EBITDA</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1483723000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1258855000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1833721000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1513760000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1370802000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Unusual Items</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>29281000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>31516000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>41092000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>51305000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>44018000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Unusual Items Excluding Goodwill</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>29281000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>31516000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>41092000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>51305000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>44018000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing Operation Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>390805000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>240528000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>698424000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>471954000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>362422000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Reconciled Depreciation</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>654669000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>635730000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>646204000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>632638000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>622566000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reconciled Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1558035000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1598618000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1768110000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1656400000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1286353000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1513004000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1290371000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1874813000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1565065000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1414820000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>858335000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>654641000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1228609000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>932427000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>792254000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Net Interest Income</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-163930000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-269475000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>-218788000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-234655000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-296385000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>379740000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>359908000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>324878000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>322074000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>329791000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>215810000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>90433000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>106090000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>87419000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>33406000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Normalized Income</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>366882423</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>214808177.489457</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>666659884</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>432295235</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>327911888</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing And Discontinued Operation</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>390805000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>240528000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>698424000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>471954000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>362422000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2597345000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2413236000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2680183000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2491424000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2146770000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Total Operating Income As Reported</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>572222000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>545708000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1119041000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>837425000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>700104000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Diluted Average Shares</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>462510666</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>458602768</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>453550895</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>445700889</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>440648342</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Basic Average Shares</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>455717833</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>451770241</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>446532648</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>439182369</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>430347768</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Diluted EPS</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Basic EPS</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Diluted NI Availto Com Stockholders</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>384916000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>235782000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>693800000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>467930000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>360760000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Net Income Common Stockholders</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>384916000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>235782000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>693800000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>467930000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>360760000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Preferred Stock Dividends</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5889000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4746000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>4624000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>4024000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1662000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>390805000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>240528000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>698424000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>471954000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>362422000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>390805000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>240528000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>698424000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>471954000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>362422000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Net Income Continuous Operations</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>390805000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>240528000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>698424000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>471954000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>362422000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tax Provision</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>87790000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>54205000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>205307000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>138399000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>100041000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pretax Income</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>478595000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>294733000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>903731000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>610353000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>462463000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Other Income Expense</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>52244000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-9317000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>7583000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>58744000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Other Non Operating Income Expenses</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>22963000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-13016000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-50409000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-43722000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>14726000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Special Income Charges</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>29281000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>31516000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>41092000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>51305000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>44018000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Other Special Charges</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-47340000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>-31516000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>-53887000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-51305000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>-44018000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Write Off</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>18059000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>12795000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Net Non Operating Interest Income Expense</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-163930000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-269475000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>-218788000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-234655000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>-296385000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Interest Expense Non Operating</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>379740000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>359908000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>324878000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>322074000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>329791000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Interest Income Non Operating</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>215810000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>90433000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>106090000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>87419000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>33406000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>590281000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>545708000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1131836000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>837425000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>700104000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>924770000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>695669000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>791254000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>724969000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>750794000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>178117000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>-6866000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>33498000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>612000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>39086000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Taxes</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>206524000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>185754000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>232371000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>201774000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>198765000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Depreciation Amortization Depletion Income Statement</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>540129000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>516781000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>525385000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>522583000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>512943000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Depreciation And Amortization In Income Statement</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>540129000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>516781000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>525385000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>522583000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>512943000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1515051000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1241377000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1923090000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1562394000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1450898000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1672575000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1717567000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1888929000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1766455000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1395976000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>3187626000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2958944000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>3812019000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>3328849000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2846874000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>3170273000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2900179000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>3812019000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>3315723000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2829597000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4518,7 +4998,1832 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>129985494</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>130864409</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>130914266</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>131102101</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>131176587</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>457832070</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>452339365</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>446596904</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>446409069</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>430774109</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>587817564</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>583203774</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>577511170</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>577511170</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>561950696</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>30487390000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>29006019000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>28931184000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>29229812000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>29411566000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>34058443000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>30934935000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>30448153000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>30405443000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>30924976000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16979159000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>16555494000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>16294120000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>15845418000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>14817615000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>51405184000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>47858011000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>47109855000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46618443000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46110287000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-349913000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-2016117000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-2232468000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-1323423000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-1087867000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>16979159000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>16590494000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>16294120000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>15845418000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>14817615000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>17346741000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>16923076000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>16661702000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>16213000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>15185311000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Preferred Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n">
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>48497656000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>44860097000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>43719821000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>44327726000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>43450190000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>17438143000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>17014167000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>16756354000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>16308940000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>15282400000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>91402000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>56091000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>94652000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>95940000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>97089000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>17346741000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16958076000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>16661702000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>16213000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>15185311000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>905000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-3006000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>30355000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>34438000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>39040000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>905000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-3006000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>30355000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>34438000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>39040000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>4725620000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>4757573000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4759386000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>4766215000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4768923000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>12790485000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>12698436000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>12752150000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>12326289000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>12116826000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>9280971000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>9020219000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>8638583000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>8618488000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>7798368000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>9280971000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>8985219000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>8638583000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8618488000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>7798368000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>58365997000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>54876563000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>53092053000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>52074200000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>51338009000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>50206025000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>47053595000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>45300828000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>45561327000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>45137754000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>938822000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>953078000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>935942000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>909408000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1151265000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Preferred Securities Outside Stock Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>219410000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>219410000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>219410000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>219410000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>219410000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>98709000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>113930000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>140266000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>180062000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>215740000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>98709000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>113930000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>140266000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>180062000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>215740000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>7723785000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>7430309000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>6625485000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>6044988000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5475442000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1818112000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1650455000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1032524000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1121559000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>696502000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>5905673000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>5779854000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>5592961000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>4923429000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>4778940000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>31150915000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>27902021000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>27058119000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>28114726000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>28264879000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>31150915000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>27902021000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>27058119000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>28114726000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>28264879000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>5467177000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>5443309000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>5367031000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>5292983000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>5236845000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>8159972000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7822968000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>7791225000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>6512873000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>6200255000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>227190000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>223240000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>259299000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>269496000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>482035000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1465906000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1127208000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>968862000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1006649000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>553694000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1465906000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1112646000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>922907000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>932712000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>468584000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2907528000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3032914000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>3390034000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2290717000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2660097000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2907528000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>3032914000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>3390034000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>2290717000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2660097000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>62170000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>63214000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>50462000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>61457000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>63156000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>3497178000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>3376392000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3122568000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2884554000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2441273000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>332904000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>285657000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>303245000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>282421000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>271149000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>332904000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>285657000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>303245000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>282421000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>271149000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>3164274000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3090735000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2819323000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2602133000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2170124000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>415455000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>525189000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>634621000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>468336000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>360233000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2748819000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2565546000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>2184702000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2133797000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1809891000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>75804140000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>71890730000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>69848407000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>68383140000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>66620409000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>67994081000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>66083879000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>64289650000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>63193690000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>61508021000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>893720000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>761082000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>705405000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1154206000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1171356000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>195008000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>187741000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>197068000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>196978000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>197960000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>22807000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>15540000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>24867000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>24777000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>25759000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>6278390000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>6425294000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>6278989000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>5917843000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>5529627000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>123226000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>124414000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>85740000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>84411000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>82896000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>6155164000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>6300880000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>6193249000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>5833432000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>5446731000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>6155164000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>6300880000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>6193249000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>5833432000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>5446731000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>367696000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>367582000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>367696000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>55368637000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>53336204000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>51754467000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>50474239000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>49140350000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>-29095973000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>-28751001000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>-28490326000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-28147570000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>-27792637000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>84464610000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>82087205000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>80244793000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>78621809000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>76932987000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>7730337000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6020008000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>5805087000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>5014935000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>4422150000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1318531000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1316280000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1206603000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>1196042000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1195989000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>7810059000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>5806851000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5558757000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>5189450000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>5112388000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>447894000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>424704000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>366482000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>327284000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>316659000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>19602000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>15898000</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>15574000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>475513000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>140630000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>86961000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>202846000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>223814000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>1883446000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1842369000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1807906000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1798643000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1703685000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1432153000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1470232000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1780439000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1665444000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1338922000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>208328000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>242402000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>250204000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>253458000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>154986000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>739153000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>703410000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>985443000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>816369000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>723616000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>-31024000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>-32324000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>-27765000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-23010000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>-17638000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>770177000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>735734000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1013208000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>839379000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>741254000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>3571053000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1928916000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1516969000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1175631000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1513410000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>3571053000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1928916000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1516969000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>1175631000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1513410000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>3502908000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>1883021000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>1434260000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>1011607000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>1444253000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>68145000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>45895000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>82709000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>164024000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>69157000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5818,7 +8123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7264,7 +9569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
